--- a/Dataset/Table_S6.xlsx
+++ b/Dataset/Table_S6.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Specificity_Paper\Supplements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soonyi/Repos/BITS_Specificity/Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A734F0B-F346-41D7-AF05-E06073789296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A647A96-F0AA-A545-A4B2-81133B4B690F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{162E82D6-14A0-4E06-BBC1-6FB27544A519}"/>
+    <workbookView xWindow="-120" yWindow="760" windowWidth="38640" windowHeight="21240" xr2:uid="{162E82D6-14A0-4E06-BBC1-6FB27544A519}"/>
   </bookViews>
   <sheets>
-    <sheet name="Model RBPs" sheetId="1" r:id="rId1"/>
+    <sheet name="Oligonucleotides" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="101">
   <si>
     <t>CLIP Oligos</t>
   </si>
@@ -322,6 +322,24 @@
   </si>
   <si>
     <t>Amplify WT RBM25</t>
+  </si>
+  <si>
+    <t>ATGCAATCgaaggctcgagaaggtatattgctgttgacagtgagcgataagcacatagtggggtttattagtgaagccacagatgtaataaaccccactatgtgcttactgcctactgcctcggaattcaagggACAATGAC</t>
+  </si>
+  <si>
+    <t>shRNA</t>
+  </si>
+  <si>
+    <t>HNRNPC_shRNA1</t>
+  </si>
+  <si>
+    <t>HNRNPC_shRNA2</t>
+  </si>
+  <si>
+    <t>ATGCAATCgaaggctcgagaaggtatattgctgttgacagtgagcgatacctaggcgcttgtctaagatagtgaagccacagatgtatcttagacaagcgcctaggtactgcctactgcctcggaattcaagggACAATGAC</t>
+  </si>
+  <si>
+    <t>shRNA flanked by XhoI/EcoRI Site</t>
   </si>
 </sst>
 </file>
@@ -388,25 +406,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -415,24 +430,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -751,504 +765,533 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ACAABC-35B9-4FF7-95E2-1B7C282BF468}">
-  <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="94.28515625" style="4" customWidth="1"/>
-    <col min="3" max="4" width="17.85546875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="14" customWidth="1"/>
-    <col min="6" max="16384" width="8.85546875" style="14"/>
+    <col min="1" max="1" width="25.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="116.6640625" style="4" customWidth="1"/>
+    <col min="3" max="4" width="17.83203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-    </row>
-    <row r="2" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="12"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="10"/>
+      <c r="D3" s="14"/>
       <c r="E3" s="2"/>
     </row>
-    <row r="4" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="10"/>
+      <c r="D4" s="14"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D5" s="16"/>
+      <c r="D5" s="13"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="17"/>
+      <c r="D7" s="15"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="12"/>
-    </row>
-    <row r="10" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D9" s="14"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="17"/>
+      <c r="D11" s="15"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D13" s="10"/>
+      <c r="D13" s="14"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="8" t="s">
+      <c r="C18" s="14"/>
+      <c r="D18" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="8" t="s">
+      <c r="C19" s="14"/>
+      <c r="D19" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="8" t="s">
+      <c r="C20" s="14"/>
+      <c r="D20" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+    <row r="21" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="8" t="s">
+      <c r="C21" s="14"/>
+      <c r="D21" s="7" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+    <row r="22" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="8" t="s">
+      <c r="C22" s="14"/>
+      <c r="D22" s="7" t="s">
         <v>27</v>
       </c>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="8" t="s">
+      <c r="C23" s="14"/>
+      <c r="D23" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+    <row r="24" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="8" t="s">
+      <c r="C24" s="14"/>
+      <c r="D24" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="8" t="s">
+      <c r="C25" s="14"/>
+      <c r="D25" s="7" t="s">
         <v>36</v>
       </c>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+    <row r="26" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="8" t="s">
+      <c r="C26" s="14"/>
+      <c r="D26" s="7" t="s">
         <v>39</v>
       </c>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+    <row r="27" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="8" t="s">
+      <c r="C27" s="14"/>
+      <c r="D27" s="7" t="s">
         <v>42</v>
       </c>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+    <row r="28" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="8" t="s">
+      <c r="C28" s="14"/>
+      <c r="D28" s="7" t="s">
         <v>45</v>
       </c>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+    <row r="29" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="8" t="s">
+      <c r="C29" s="14"/>
+      <c r="D29" s="7" t="s">
         <v>12</v>
       </c>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+    <row r="30" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="8" t="s">
+      <c r="C30" s="14"/>
+      <c r="D30" s="7" t="s">
         <v>49</v>
       </c>
       <c r="E30" s="2"/>
     </row>
-    <row r="31" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+    <row r="31" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="8" t="s">
+      <c r="C31" s="14"/>
+      <c r="D31" s="7" t="s">
         <v>52</v>
       </c>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+    <row r="32" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="8" t="s">
+      <c r="C32" s="14"/>
+      <c r="D32" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E32" s="2"/>
     </row>
-    <row r="33" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+    <row r="33" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="8" t="s">
+      <c r="C33" s="14"/>
+      <c r="D33" s="7" t="s">
         <v>58</v>
       </c>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+    <row r="34" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C34" s="10"/>
-      <c r="D34" s="8" t="s">
+      <c r="C34" s="14"/>
+      <c r="D34" s="7" t="s">
         <v>61</v>
       </c>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+    <row r="35" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="8" t="s">
+      <c r="C35" s="14"/>
+      <c r="D35" s="7" t="s">
         <v>64</v>
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" spans="1:5" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+    <row r="36" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="8" t="s">
+      <c r="C36" s="14"/>
+      <c r="D36" s="7" t="s">
         <v>67</v>
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
       <c r="E37" s="2"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="14"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="12"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>100</v>
+      </c>
       <c r="D39" s="14"/>
     </row>
+    <row r="40" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="14"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C5:D6"/>
-    <mergeCell ref="C9:D10"/>
-    <mergeCell ref="C11:D12"/>
-    <mergeCell ref="C13:D13"/>
+  <mergeCells count="15">
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="C17:C36"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C7:D8"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C5:D6"/>
+    <mergeCell ref="C9:D10"/>
+    <mergeCell ref="C11:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
